--- a/ROSA_vitaSPEC/Data/Analyses_chimiques_new_HR.xlsx
+++ b/ROSA_vitaSPEC/Data/Analyses_chimiques_new_HR.xlsx
@@ -387,7 +387,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>FFA(%)</t>
+          <t>FFA</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
